--- a/product_selector_out/STM32WBAxM modules.xlsx
+++ b/product_selector_out/STM32WBAxM modules.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP12"/>
+  <dimension ref="A1:BQ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.953125" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1005,6 +1011,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1344,12 +1351,17 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba5mmg.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -1372,14 +1384,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -1397,6 +1408,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -1409,6 +1421,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -1432,7 +1445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP12"/>
+  <dimension ref="A1:BQ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1503,6 +1516,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1851,6 +1865,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1949,6 +1968,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2286,7 +2306,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
+      <c r="BP12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -2294,8 +2319,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
